--- a/xls/square_high_un_16_tri3_11.xlsx
+++ b/xls/square_high_un_16_tri3_11.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>340</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>618</v>
+      </c>
+      <c r="I9">
+        <v>0.24927948686776757</v>
+      </c>
+      <c r="J9">
+        <v>-0.8118659854005443</v>
+      </c>
+      <c r="K9">
+        <v>-0.08855935692839756</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>174</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>340</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>165</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>864</v>
+      </c>
+      <c r="I10">
+        <v>-1.6709783559685698</v>
+      </c>
+      <c r="J10">
+        <v>-1.7010313433409727</v>
+      </c>
+      <c r="K10">
+        <v>-0.7176562918331025</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
